--- a/data/內運週二團第二季試辦比賽.xlsx
+++ b/data/內運週二團第二季試辦比賽.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n1025\Desktop\NBA 選秀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n1025\Desktop\NBA選秀\NBA-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C59851-8EF7-401C-B729-081CAE796A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F77D523-3BC4-4E14-BF04-ED91A9F88DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24765" yWindow="2490" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEUTEC 組隊報名區" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>Neil</t>
   </si>
   <si>
-    <t>Paul (DI)</t>
-  </si>
-  <si>
     <t>Glenn</t>
   </si>
   <si>
@@ -121,6 +118,10 @@
     <t>幾星</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>Paul(DI)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -129,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -189,6 +190,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -210,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -228,6 +236,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -235,7 +247,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -464,16 +475,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -493,7 +504,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -597,7 +608,7 @@
       <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <v>3</v>
       </c>
     </row>
@@ -653,8 +664,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>19</v>
+      <c r="A13" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>6</v>
@@ -672,13 +683,13 @@
     </row>
     <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>7</v>
@@ -690,13 +701,13 @@
     </row>
     <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>7</v>
@@ -707,7 +718,7 @@
     </row>
     <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>6</v>
@@ -725,7 +736,7 @@
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
@@ -736,13 +747,13 @@
       <c r="D17" s="6">
         <v>46203</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
@@ -753,13 +764,13 @@
       <c r="D18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
@@ -777,7 +788,7 @@
     </row>
     <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
@@ -825,11 +836,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="A1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
@@ -873,7 +884,7 @@
     </row>
     <row r="8" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>

--- a/data/內運週二團第二季試辦比賽.xlsx
+++ b/data/內運週二團第二季試辦比賽.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n1025\Desktop\NBA選秀\NBA-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F77D523-3BC4-4E14-BF04-ED91A9F88DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BBA9E3-4AED-49AA-8B40-C812ED880F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24765" yWindow="2490" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEUTEC 組隊報名區" sheetId="1" r:id="rId1"/>
@@ -695,7 +695,7 @@
         <v>7</v>
       </c>
       <c r="E14" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1"/>
     </row>

--- a/data/內運週二團第二季試辦比賽.xlsx
+++ b/data/內運週二團第二季試辦比賽.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n1025\Desktop\NBA選秀\NBA-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BBA9E3-4AED-49AA-8B40-C812ED880F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA514AEF-1412-44DC-8743-A29B19C0EA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1"/>
     </row>

--- a/data/內運週二團第二季試辦比賽.xlsx
+++ b/data/內運週二團第二季試辦比賽.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n1025\Desktop\NBA選秀\NBA-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA514AEF-1412-44DC-8743-A29B19C0EA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBEF306-FA54-4C30-8EDF-C7CFA235D666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEUTEC 組隊報名區" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="35">
   <si>
     <t>*預計組二隊，一隊最少 5 人，最多 8 人，方便累的時侯可以換人
 *6/23 第一輪四隊輪打，一場 12 分鐘，如果報名完只有三隊會再調整比賽時長
@@ -122,6 +122,26 @@
     <t>Paul(DI)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>鋒線</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>18:00 ~ 19:00</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>James</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>後衛</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kai</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -130,7 +150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -197,6 +217,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -218,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -247,6 +274,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -465,9 +494,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -585,8 +615,8 @@
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
+      <c r="C8" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>7</v>
@@ -768,12 +798,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
+      <c r="B19" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>7</v>
@@ -786,12 +816,12 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>9</v>
+      <c r="B20" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>7</v>
@@ -803,6 +833,40 @@
         <v>3</v>
       </c>
       <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46196</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46196</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -810,13 +874,13 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4:B20" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4:B22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"後衛,鋒線,中鋒"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4:C20" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4:C22" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"全程,18:00 ~ 19:00,19:00 ~ 20:00"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D20" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D22" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"全程,06/23,06/30"</formula1>
     </dataValidation>
   </dataValidations>
